--- a/output/PRM/reports/prm_report.xlsx
+++ b/output/PRM/reports/prm_report.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="11_098EED5A1D5F09C1576831A6AB027DD31165DE90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5B438F4-2786-4CA9-84F4-8EE33DEDE072}"/>
   <bookViews>
-    <workbookView xWindow="7005" yWindow="5535" windowWidth="38700" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16710" yWindow="8115" windowWidth="38700" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monthly_PRMs" sheetId="1" r:id="rId1"/>
